--- a/题库/PY程序设计模拟题4.xlsx
+++ b/题库/PY程序设计模拟题4.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="132">
   <si>
     <t>题号</t>
   </si>
@@ -378,10 +378,13 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">P y t h o n </t>
+  </si>
+  <si>
     <t>P, y, t, h, o, n,</t>
   </si>
   <si>
-    <t>P y t h o n</t>
+    <t>P  y  t  h  o  n</t>
   </si>
   <si>
     <t>下列Python数据中，其元素可以改变的是（）。</t>
@@ -521,6 +524,9 @@
   </si>
   <si>
     <t>表达式'abc'in('abcdefg')的值为【1】。</t>
+  </si>
+  <si>
+    <t>True</t>
   </si>
   <si>
     <t>表达式':'.join('hello world'.split())的值为【1】。</t>
@@ -2480,14 +2486,14 @@
       <c r="C23" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>65</v>
+      <c r="D23" s="3" t="s">
+        <v>68</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>65</v>
@@ -2504,7 +2510,7 @@
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="6"/>
-      <c r="D24" s="2"/>
+      <c r="D24" s="3"/>
       <c r="E24" s="2"/>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
@@ -2516,7 +2522,7 @@
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="7"/>
-      <c r="D25" s="2"/>
+      <c r="D25" s="3"/>
       <c r="E25" s="2"/>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
@@ -2532,19 +2538,19 @@
         <v>10</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>16</v>
@@ -2562,7 +2568,7 @@
         <v>10</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D27" s="2">
         <v>29</v>
@@ -2571,7 +2577,7 @@
         <v>28</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G27" s="2">
         <v>28.27</v>
@@ -2616,19 +2622,19 @@
         <v>10</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>22</v>
@@ -2640,7 +2646,7 @@
     </row>
     <row r="31" ht="17" spans="1:10">
       <c r="A31" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
@@ -2657,10 +2663,10 @@
         <v>16</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D32" s="2"/>
       <c r="E32" s="2"/>
@@ -2679,17 +2685,17 @@
         <v>17</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D33" s="2"/>
       <c r="E33" s="2"/>
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
       <c r="H33" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I33" s="2">
         <v>2</v>
@@ -2701,17 +2707,17 @@
         <v>18</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D34" s="2"/>
       <c r="E34" s="2"/>
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
       <c r="H34" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I34" s="2">
         <v>2</v>
@@ -2723,17 +2729,17 @@
         <v>19</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D35" s="2"/>
       <c r="E35" s="2"/>
       <c r="F35" s="2"/>
       <c r="G35" s="2"/>
       <c r="H35" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I35" s="2">
         <v>2</v>
@@ -2745,17 +2751,17 @@
         <v>20</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D36" s="2"/>
       <c r="E36" s="2"/>
       <c r="F36" s="2"/>
       <c r="G36" s="2"/>
       <c r="H36" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I36" s="2">
         <v>2</v>
@@ -2767,17 +2773,17 @@
         <v>21</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D37" s="2"/>
       <c r="E37" s="2"/>
       <c r="F37" s="2"/>
       <c r="G37" s="2"/>
       <c r="H37" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I37" s="2">
         <v>2</v>
@@ -2789,10 +2795,10 @@
         <v>22</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D38" s="2"/>
       <c r="E38" s="2"/>
@@ -2811,10 +2817,10 @@
         <v>23</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D39" s="2"/>
       <c r="E39" s="2"/>
@@ -2869,10 +2875,10 @@
         <v>24</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D43" s="2"/>
       <c r="E43" s="2"/>
@@ -2891,17 +2897,17 @@
         <v>25</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D44" s="2"/>
       <c r="E44" s="2"/>
       <c r="F44" s="2"/>
       <c r="G44" s="2"/>
       <c r="H44" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I44" s="2">
         <v>2</v>
@@ -2913,17 +2919,17 @@
         <v>26</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D45" s="2"/>
       <c r="E45" s="2"/>
       <c r="F45" s="2"/>
       <c r="G45" s="2"/>
-      <c r="H45" s="2" t="b">
-        <v>1</v>
+      <c r="H45" s="3" t="s">
+        <v>101</v>
       </c>
       <c r="I45" s="2">
         <v>2</v>
@@ -2935,17 +2941,17 @@
         <v>27</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D46" s="2"/>
       <c r="E46" s="2"/>
       <c r="F46" s="2"/>
       <c r="G46" s="2"/>
       <c r="H46" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="I46" s="2">
         <v>2</v>
@@ -2957,10 +2963,10 @@
         <v>28</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D47" s="2"/>
       <c r="E47" s="2"/>
@@ -2979,17 +2985,17 @@
         <v>29</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D48" s="2"/>
       <c r="E48" s="2"/>
       <c r="F48" s="2"/>
       <c r="G48" s="2"/>
       <c r="H48" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="I48" s="2">
         <v>2</v>
@@ -3001,10 +3007,10 @@
         <v>30</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D49" s="2"/>
       <c r="E49" s="2"/>
@@ -3020,7 +3026,7 @@
     </row>
     <row r="50" ht="17" spans="1:10">
       <c r="A50" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
@@ -3037,16 +3043,16 @@
         <v>31</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="F51" s="2"/>
       <c r="G51" s="2"/>
@@ -3063,16 +3069,16 @@
         <v>32</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C52" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D52" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="D52" s="2" t="s">
-        <v>108</v>
-      </c>
       <c r="E52" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="F52" s="2"/>
       <c r="G52" s="2"/>
@@ -3089,16 +3095,16 @@
         <v>33</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C53" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E53" s="2" t="s">
         <v>111</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>109</v>
       </c>
       <c r="F53" s="2"/>
       <c r="G53" s="2"/>
@@ -3115,16 +3121,16 @@
         <v>34</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="F54" s="2"/>
       <c r="G54" s="2"/>
@@ -3141,16 +3147,16 @@
         <v>35</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="F55" s="2"/>
       <c r="G55" s="2"/>
@@ -3167,16 +3173,16 @@
         <v>36</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="F56" s="2"/>
       <c r="G56" s="2"/>
@@ -3193,16 +3199,16 @@
         <v>37</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="F57" s="2"/>
       <c r="G57" s="2"/>
@@ -3219,16 +3225,16 @@
         <v>38</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="F58" s="2"/>
       <c r="G58" s="2"/>
@@ -3245,16 +3251,16 @@
         <v>39</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="F59" s="2"/>
       <c r="G59" s="2"/>
@@ -3271,16 +3277,16 @@
         <v>40</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="F60" s="2"/>
       <c r="G60" s="2"/>
@@ -3294,7 +3300,7 @@
     </row>
     <row r="61" ht="17" spans="1:10">
       <c r="A61" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
@@ -3311,23 +3317,23 @@
         <v>41</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D62" s="2"/>
       <c r="E62" s="2"/>
       <c r="F62" s="2"/>
       <c r="G62" s="2"/>
       <c r="H62" s="9" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="I62" s="2">
         <v>10</v>
       </c>
       <c r="J62" s="10" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="63" ht="119" spans="1:10">
@@ -3335,28 +3341,28 @@
         <v>42</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D63" s="2"/>
       <c r="E63" s="2"/>
       <c r="F63" s="2"/>
       <c r="G63" s="2"/>
       <c r="H63" s="9" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="I63" s="2">
         <v>10</v>
       </c>
       <c r="J63" s="10" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="64" ht="17" spans="1:10">
       <c r="A64" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
@@ -3373,23 +3379,23 @@
         <v>43</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D65" s="2"/>
       <c r="E65" s="2"/>
       <c r="F65" s="2"/>
       <c r="G65" s="2"/>
       <c r="H65" s="9" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="I65" s="2">
         <v>10</v>
       </c>
       <c r="J65" s="10" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>
